--- a/interface-agreements/source/Workday-HCM/v1.0/Interface Agreement - Batch Template.xlsx
+++ b/interface-agreements/source/Workday-HCM/v1.0/Interface Agreement - Batch Template.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prateek.nichani\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D2275E-A62C-498F-847E-21EB0B61B394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F436351C-204E-4545-A28C-2E7AEF97AA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Integration" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="279">
   <si>
     <t xml:space="preserve">Interface Agreement Specification · Complete one per system · Blue = fill in </t>
   </si>
@@ -1201,16 +1201,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1244,9 +1238,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1259,21 +1250,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1300,43 +1276,109 @@
     <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{2BA128E2-6384-40D9-A463-F0657219D3C7}"/>
@@ -1423,6 +1465,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1614,757 +1660,791 @@
     <col min="2" max="2" width="34.54296875" customWidth="1"/>
     <col min="3" max="3" width="45.1796875" customWidth="1"/>
     <col min="4" max="4" width="33.7265625" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="31" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="36"/>
+    </row>
     <row r="13" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="36"/>
+    </row>
     <row r="22" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="46"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="3" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="3" t="s">
+      <c r="B26" s="20"/>
+      <c r="C26" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="3" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="36"/>
+    </row>
     <row r="29" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="41" t="str">
+      <c r="A29" s="47" t="str">
         <f>"3 A. INTEGRATION DESIGN - SPECIFIC TO " &amp; UPPER(IF(ISBLANK($B$23), "Integration Pattern", $B$23))</f>
         <v>3 A. INTEGRATION DESIGN - SPECIFIC TO BATCH FILE</v>
       </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="46"/>
     </row>
     <row r="30" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="3" t="s">
+      <c r="B30" s="20"/>
+      <c r="C30" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="39" t="s">
         <v>128</v>
       </c>
+      <c r="E30" s="36"/>
     </row>
     <row r="31" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3" t="s">
+      <c r="B31" s="20"/>
+      <c r="C31" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="39" t="s">
         <v>133</v>
       </c>
+      <c r="E31" s="36"/>
     </row>
     <row r="32" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="39" t="s">
         <v>136</v>
       </c>
+      <c r="E32" s="36"/>
     </row>
     <row r="33" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="39" t="s">
         <v>139</v>
       </c>
+      <c r="E33" s="36"/>
     </row>
     <row r="34" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="3" t="s">
+      <c r="B34" s="20"/>
+      <c r="C34" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="D34" s="16" t="str">
+      <c r="D34" s="39" t="str">
         <f>IFERROR(INDEX(#REF!, MATCH('1. Data Integration'!$B$23&amp;"|"&amp;11,#REF!, 0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="E34" s="36"/>
+    </row>
+    <row r="35" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="38"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="36"/>
+    </row>
     <row r="36" spans="1:5" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="40"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="46"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="26"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="36"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="3" t="s">
+      <c r="B39" s="20"/>
+      <c r="C39" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="3" t="s">
+      <c r="B40" s="20"/>
+      <c r="C40" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="3" t="s">
+      <c r="B41" s="20"/>
+      <c r="C41" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="3" t="s">
+      <c r="B42" s="20"/>
+      <c r="C42" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="26" t="s">
+      <c r="D42" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="38"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="36"/>
+    </row>
     <row r="44" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="44" t="s">
+      <c r="A44" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="40"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="46"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="26" t="s">
+      <c r="D45" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="26" t="s">
+      <c r="D47" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="D48" s="26" t="s">
+      <c r="D48" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="D49" s="26" t="s">
+      <c r="D49" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="D50" s="26" t="s">
+      <c r="D50" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="26" t="s">
+      <c r="D51" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="B52" s="7" t="b">
+      <c r="B52" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="D52" s="26" t="b">
+      <c r="D52" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="40"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="45"/>
+      <c r="E53" s="46"/>
     </row>
     <row r="54" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="D54" s="26" t="s">
+      <c r="D54" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="D55" s="26" t="s">
+      <c r="D55" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A22:E22"/>
@@ -2395,7 +2475,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2428,176 +2508,176 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
     </row>
     <row r="3" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="M3" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="23" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:16" s="17" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="19">
         <v>1</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="J5" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="K5" s="22" t="b">
+      <c r="J5" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="K5" s="19" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="19" t="s">
         <v>130</v>
       </c>
       <c r="O5" t="s">
@@ -2661,1151 +2741,1151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:11" s="17" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="21"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="19">
         <v>1</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G5" s="22" t="s">
+      <c r="F5" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J5" s="22" t="s">
+      <c r="I5" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="19">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J6" s="22" t="s">
+      <c r="I6" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>3</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="22" t="s">
+      <c r="F7" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="I7" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J7" s="22" t="s">
+      <c r="I7" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="19">
         <v>4</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G8" s="22" t="s">
+      <c r="F8" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="22" t="s">
+      <c r="I8" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="19">
         <v>5</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G9" s="22" t="s">
+      <c r="F9" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J9" s="22" t="s">
+      <c r="I9" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="19">
         <v>6</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G10" s="22" t="s">
+      <c r="F10" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G10" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J10" s="22" t="s">
+      <c r="I10" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="19">
         <v>7</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F11" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G11" s="22" t="s">
+      <c r="F11" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J11" s="22" t="s">
+      <c r="I11" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J11" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="19">
         <v>8</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G12" s="22" t="s">
+      <c r="F12" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I12" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J12" s="22" t="s">
+      <c r="I12" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="19">
         <v>9</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G13" s="22" t="s">
+      <c r="F13" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I13" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J13" s="22" t="s">
+      <c r="I13" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J13" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="19">
         <v>10</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" s="22" t="s">
+      <c r="F14" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I14" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="22" t="s">
+      <c r="I14" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="19">
         <v>11</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F15" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G15" s="22" t="s">
+      <c r="F15" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I15" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J15" s="22" t="s">
+      <c r="I15" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J15" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="19">
         <v>12</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="F16" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G16" s="22" t="s">
+      <c r="F16" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="I16" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J16" s="22" t="s">
+      <c r="I16" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="19">
         <v>13</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G17" s="22" t="s">
+      <c r="F17" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I17" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J17" s="22" t="s">
+      <c r="I17" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J17" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="19">
         <v>14</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G18" s="22" t="s">
+      <c r="F18" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="I18" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J18" s="22" t="s">
+      <c r="I18" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="19">
         <v>15</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F19" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G19" s="22" t="s">
+      <c r="F19" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="I19" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J19" s="22" t="s">
+      <c r="I19" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J19" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="19">
         <v>16</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="F20" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G20" s="22" t="s">
+      <c r="F20" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="I20" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J20" s="22" t="s">
+      <c r="I20" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J20" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="19">
         <v>17</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="F21" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="I21" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J21" s="22" t="s">
+      <c r="I21" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J21" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="19">
         <v>18</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F22" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G22" s="22" t="s">
+      <c r="F22" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G22" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="I22" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="I22" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J22" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="19">
         <v>19</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G23" s="22" t="s">
+      <c r="F23" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I23" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="22" t="s">
+      <c r="I23" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="19">
         <v>20</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F24" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G24" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I24" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J24" s="22" t="s">
+      <c r="I24" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J24" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="19">
         <v>21</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F25" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G25" s="22" t="s">
+      <c r="F25" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I25" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J25" s="22" t="s">
+      <c r="I25" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J25" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="19">
         <v>22</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G26" s="22" t="s">
+      <c r="F26" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I26" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J26" s="22" t="s">
+      <c r="I26" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="19">
         <v>23</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G27" s="22" t="s">
+      <c r="F27" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G27" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I27" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J27" s="22" t="s">
+      <c r="I27" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="19">
         <v>24</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G28" s="22" t="s">
+      <c r="F28" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I28" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J28" s="22" t="s">
+      <c r="I28" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J28" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="19">
         <v>25</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G29" s="22" t="s">
+      <c r="F29" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G29" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I29" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J29" s="22" t="s">
+      <c r="I29" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J29" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="19">
         <v>26</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I30" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J30" s="22" t="s">
+      <c r="I30" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J30" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="19">
         <v>27</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F31" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G31" s="22" t="s">
+      <c r="F31" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="I31" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J31" s="22" t="s">
+      <c r="I31" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J31" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="19">
         <v>28</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F32" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G32" s="22" t="s">
+      <c r="F32" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I32" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J32" s="22" t="s">
+      <c r="I32" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J32" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="19">
         <v>29</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G33" s="22" t="s">
+      <c r="F33" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G33" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="I33" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J33" s="22" t="s">
+      <c r="I33" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J33" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="19">
         <v>30</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="F34" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G34" s="22" t="s">
+      <c r="F34" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G34" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="I34" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J34" s="22" t="s">
+      <c r="I34" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J34" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="19">
         <v>31</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G35" s="22" t="s">
+      <c r="F35" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G35" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="I35" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J35" s="22" t="s">
+      <c r="I35" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J35" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="19">
         <v>32</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="F36" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G36" s="22" t="s">
+      <c r="F36" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="I36" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J36" s="22" t="s">
+      <c r="I36" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J36" s="19" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="19">
         <v>33</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="F37" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G37" s="22" t="s">
+      <c r="F37" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G37" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="I37" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="J37" s="22" t="s">
+      <c r="I37" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J37" s="19" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3823,143 +3903,143 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.453125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.54296875" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" style="3" customWidth="1"/>
     <col min="4" max="4" width="32.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>164</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>166</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
+    <row r="4" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
         <v>46248</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="6"/>
+    <row r="5" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="7"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="7"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3982,36 +4062,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="25" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="35" t="str">
-        <f>'1. Data Integration'!B3</f>
+      <c r="B3" s="27" t="str">
+        <f>IF('1. Data Integration'!B3="","",'1. Data Integration'!B3)</f>
         <v>DSI116-A906-Workday HCM</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="26" t="s">
         <v>227</v>
       </c>
       <c r="D3" t="s">
@@ -4019,14 +4099,14 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="B4" s="35" t="str">
-        <f>'1. Data Integration'!B5</f>
-        <v>Workday HCM</v>
-      </c>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="27" t="str">
+        <f>IF('1. Data Integration'!B5="","",'1. Data Integration'!B5)</f>
+        <v/>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
@@ -4034,86 +4114,86 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="35" t="str">
-        <f>'1. Data Integration'!B6</f>
+      <c r="B5" s="27" t="str">
+        <f>IF('1. Data Integration'!B6="","",'1. Data Integration'!B6)</f>
         <v>A906</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="26" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="35" t="str">
-        <f>'1. Data Integration'!B7</f>
+      <c r="B6" s="27" t="str">
+        <f>IF('1. Data Integration'!B7="","",'1. Data Integration'!B7)</f>
         <v>WD</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="B7" s="35" t="str">
-        <f>'1. Data Integration'!B8</f>
+      <c r="B7" s="27" t="str">
+        <f>IF('1. Data Integration'!B8="","",'1. Data Integration'!B8)</f>
         <v>Workday Inc</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="26" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="35" t="str">
-        <f>'1. Data Integration'!B11</f>
+      <c r="B8" s="27" t="str">
+        <f>IF('1. Data Integration'!B11="","",'1. Data Integration'!B11)</f>
         <v>People, Finance</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="B9" s="35" t="str">
-        <f>'1. Data Integration'!B14</f>
+      <c r="B9" s="27" t="str">
+        <f>IF('1. Data Integration'!B14="","",'1. Data Integration'!B14)</f>
         <v>Bill Smith</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="26" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="B10" s="35" t="str">
-        <f>'1. Data Integration'!B15</f>
+      <c r="B10" s="27" t="str">
+        <f>IF('1. Data Integration'!B15="","",'1. Data Integration'!B15)</f>
         <v>People Analytics Manager; Nicole Smith</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="26" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="B11" s="35" t="str">
-        <f>'1. Data Integration'!B23</f>
+      <c r="B11" s="27" t="str">
+        <f>IF('1. Data Integration'!B23="","",'1. Data Integration'!B23)</f>
         <v>Batch File</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="26" t="s">
         <v>58</v>
       </c>
       <c r="D11" t="s">
@@ -4121,14 +4201,14 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="B12" s="35" t="str">
-        <f>'1. Data Integration'!B24</f>
+      <c r="B12" s="27" t="str">
+        <f>IF('1. Data Integration'!B24="","",'1. Data Integration'!B24)</f>
         <v>Push</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="26" t="s">
         <v>61</v>
       </c>
       <c r="D12" t="s">
@@ -4145,6 +4225,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="a207430b-1728-4bb6-9221-c16b18b91a04">
@@ -4155,7 +4244,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B3F6CA5DA94C54DBDF5B4FCF2C6B6C5" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="489ee38bad4e4aadf0e4ba8271dd1ea7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a207430b-1728-4bb6-9221-c16b18b91a04" xmlns:ns3="aca2c1e6-caa4-4574-b5ed-1eed0ddc62d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="16c0c607a85bcaecc1d5ad9b60430e5a" ns2:_="" ns3:_="">
     <xsd:import namespace="a207430b-1728-4bb6-9221-c16b18b91a04"/>
@@ -4362,16 +4451,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29206025-1A77-49E8-8202-972156E9F071}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{429401C2-5A1E-4D9B-B9A0-FEBD8BCEFCDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -4388,7 +4476,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52F56BCF-43E6-4EDD-A7CB-0CFE3F90AED4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4405,12 +4493,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29206025-1A77-49E8-8202-972156E9F071}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/interface-agreements/source/Workday-HCM/v1.0/Interface Agreement - Batch Template.xlsx
+++ b/interface-agreements/source/Workday-HCM/v1.0/Interface Agreement - Batch Template.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prateek.nichani\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F436351C-204E-4545-A28C-2E7AEF97AA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74F8C1-CE5B-49AD-9868-18294DB73E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Integration" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="281">
   <si>
     <t xml:space="preserve">Interface Agreement Specification · Complete one per system · Blue = fill in </t>
   </si>
@@ -883,13 +883,19 @@
   </si>
   <si>
     <t>Dataset Name</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>File Naming Convention (Mandatory)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1017,6 +1023,13 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1201,7 +1214,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1379,6 +1392,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{2BA128E2-6384-40D9-A463-F0657219D3C7}"/>
@@ -1465,10 +1481,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1719,7 +1731,9 @@
       <c r="A5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="C5" s="34" t="s">
         <v>12</v>
       </c>
@@ -2625,8 +2639,8 @@
       <c r="I4" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="J4" s="10" t="s">
-        <v>247</v>
+      <c r="J4" s="58" t="s">
+        <v>280</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>259</v>
@@ -2847,7 +2861,7 @@
         <v>170</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>172</v>
@@ -4104,7 +4118,7 @@
       </c>
       <c r="B4" s="27" t="str">
         <f>IF('1. Data Integration'!B5="","",'1. Data Integration'!B5)</f>
-        <v/>
+        <v>Workday HCM</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>10</v>
@@ -4225,26 +4239,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a207430b-1728-4bb6-9221-c16b18b91a04">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aca2c1e6-caa4-4574-b5ed-1eed0ddc62d5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B3F6CA5DA94C54DBDF5B4FCF2C6B6C5" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="489ee38bad4e4aadf0e4ba8271dd1ea7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a207430b-1728-4bb6-9221-c16b18b91a04" xmlns:ns3="aca2c1e6-caa4-4574-b5ed-1eed0ddc62d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="16c0c607a85bcaecc1d5ad9b60430e5a" ns2:_="" ns3:_="">
     <xsd:import namespace="a207430b-1728-4bb6-9221-c16b18b91a04"/>
@@ -4451,10 +4445,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a207430b-1728-4bb6-9221-c16b18b91a04">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aca2c1e6-caa4-4574-b5ed-1eed0ddc62d5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29206025-1A77-49E8-8202-972156E9F071}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52F56BCF-43E6-4EDD-A7CB-0CFE3F90AED4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a207430b-1728-4bb6-9221-c16b18b91a04"/>
+    <ds:schemaRef ds:uri="aca2c1e6-caa4-4574-b5ed-1eed0ddc62d5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4477,20 +4502,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52F56BCF-43E6-4EDD-A7CB-0CFE3F90AED4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29206025-1A77-49E8-8202-972156E9F071}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a207430b-1728-4bb6-9221-c16b18b91a04"/>
-    <ds:schemaRef ds:uri="aca2c1e6-caa4-4574-b5ed-1eed0ddc62d5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>